--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1287,6 +1287,3017 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130261234</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57985</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>759386</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7074195</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130261223</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91692</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>759450</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7074279</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130261227</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91728</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>759410</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7074242</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Granlåga rotknäckt</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga rotknäckt</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130261236</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>759588</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7074157</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Granhögstubbe grov, knäckt</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe grov, knäckt</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130261249</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58198</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>759466</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7074152</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130261225</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91692</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>759453</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7074313</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Tunnare granlåga invid äldre talltorraka</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies # Tunnare granlåga invid äldre talltorraka</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130261241</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>759358</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7074193</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Granlåga, knäckt</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga, knäckt</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130261254</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91724</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>759629</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7074125</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Stående död</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130261257</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91724</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>759449</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7074314</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Stående död</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130261233</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57985</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>759425</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7074122</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130261224</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91692</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>759568</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7074103</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Äldre granlåga</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre granlåga</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130261235</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>759616</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7074094</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Granhögstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130261256</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91724</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>759454</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7074134</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Granstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies # Granstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130261239</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>759521</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7074165</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies # Levande</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130261231</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>759348</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7074185</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på granlåga</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130261237</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>759528</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7074150</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Högt upp</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies # Levande</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130261242</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>759521</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7074133</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Knäckt gran</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies # Knäckt gran</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130261226</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91692</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>759410</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7074242</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Granlåga rotknäckt</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga rotknäckt</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130261243</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>759457</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7074149</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Kåda</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130261255</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91724</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>759576</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7074103</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>Granstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies # Granstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130261258</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91724</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>759498</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7074364</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>Stående död</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130261240</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>759411</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7074135</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies # Levande</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130261259</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91724</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>759622</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7074145</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>Stående död</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130261228</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>759417</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7074118</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>Stående död</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130261238</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>759413</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7074262</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies # Levande</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -1764,50 +1764,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130261241</v>
+        <v>130261225</v>
       </c>
       <c r="B11" t="n">
-        <v>57823</v>
+        <v>91692</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759358</v>
+        <v>759453</v>
       </c>
       <c r="R11" t="n">
-        <v>7074193</v>
+        <v>7074313</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1863,12 +1858,12 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt</t>
+          <t>Tunnare granlåga invid äldre talltorraka</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies # Tunnare granlåga invid äldre talltorraka</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1886,27 +1881,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130261249</v>
+        <v>130261241</v>
       </c>
       <c r="B12" t="n">
-        <v>58198</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1915,24 +1910,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759466</v>
+        <v>759358</v>
       </c>
       <c r="R12" t="n">
-        <v>7074152</v>
+        <v>7074193</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1962,21 +1954,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1985,6 +1967,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Granlåga, knäckt</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga, knäckt</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2001,10 +2003,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130261225</v>
+        <v>130261249</v>
       </c>
       <c r="B13" t="n">
-        <v>91692</v>
+        <v>58198</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,34 +2014,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759453</v>
+        <v>759466</v>
       </c>
       <c r="R13" t="n">
-        <v>7074313</v>
+        <v>7074152</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2069,11 +2079,21 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2082,26 +2102,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Tunnare granlåga invid äldre talltorraka</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies # Tunnare granlåga invid äldre talltorraka</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2950,45 +2950,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130261226</v>
+        <v>130261242</v>
       </c>
       <c r="B21" t="n">
-        <v>91692</v>
+        <v>57823</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759410</v>
+        <v>759521</v>
       </c>
       <c r="R21" t="n">
-        <v>7074242</v>
+        <v>7074133</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3023,6 +3028,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3044,12 +3054,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Granlåga rotknäckt</t>
+          <t>Knäckt gran</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga rotknäckt</t>
+          <t>Picea abies # Knäckt gran</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3067,10 +3077,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130261231</v>
+        <v>130261237</v>
       </c>
       <c r="B22" t="n">
-        <v>57826</v>
+        <v>57823</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3078,16 +3088,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3107,10 +3117,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759348</v>
+        <v>759528</v>
       </c>
       <c r="R22" t="n">
-        <v>7074185</v>
+        <v>7074150</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3147,7 +3157,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på granlåga</t>
+          <t>Högt upp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3171,12 +3181,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3194,10 +3204,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130261242</v>
+        <v>130261231</v>
       </c>
       <c r="B23" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3205,16 +3215,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3234,10 +3244,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759521</v>
+        <v>759348</v>
       </c>
       <c r="R23" t="n">
-        <v>7074133</v>
+        <v>7074185</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3274,7 +3284,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Vid basen</t>
+          <t>Ringhack på granlåga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3298,12 +3308,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Knäckt gran</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Knäckt gran</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3321,50 +3331,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130261237</v>
+        <v>130261226</v>
       </c>
       <c r="B24" t="n">
-        <v>57823</v>
+        <v>91692</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759528</v>
+        <v>759410</v>
       </c>
       <c r="R24" t="n">
-        <v>7074150</v>
+        <v>7074242</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3399,11 +3404,6 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Högt upp</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3425,12 +3425,12 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granlåga rotknäckt</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granlåga rotknäckt</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -1764,45 +1764,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130261225</v>
+        <v>130261241</v>
       </c>
       <c r="B11" t="n">
-        <v>91692</v>
+        <v>57823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759453</v>
+        <v>759358</v>
       </c>
       <c r="R11" t="n">
-        <v>7074313</v>
+        <v>7074193</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1858,12 +1863,12 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>Tunnare granlåga invid äldre talltorraka</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies # Tunnare granlåga invid äldre talltorraka</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1881,27 +1886,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130261241</v>
+        <v>130261249</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>58198</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1910,21 +1915,24 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759358</v>
+        <v>759466</v>
       </c>
       <c r="R12" t="n">
-        <v>7074193</v>
+        <v>7074152</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1954,11 +1962,21 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1967,26 +1985,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Granlåga, knäckt</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga, knäckt</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2003,10 +2001,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130261249</v>
+        <v>130261225</v>
       </c>
       <c r="B13" t="n">
-        <v>58198</v>
+        <v>91692</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,42 +2012,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759466</v>
+        <v>759453</v>
       </c>
       <c r="R13" t="n">
-        <v>7074152</v>
+        <v>7074313</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2079,21 +2069,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2102,6 +2082,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Tunnare granlåga invid äldre talltorraka</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies # Tunnare granlåga invid äldre talltorraka</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2357,45 +2357,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130261224</v>
+        <v>130261233</v>
       </c>
       <c r="B16" t="n">
-        <v>91692</v>
+        <v>57985</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759568</v>
+        <v>759425</v>
       </c>
       <c r="R16" t="n">
-        <v>7074103</v>
+        <v>7074122</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2425,11 +2433,21 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2438,26 +2456,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Äldre granlåga</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre granlåga</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2474,50 +2472,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130261235</v>
+        <v>130261224</v>
       </c>
       <c r="B17" t="n">
-        <v>57823</v>
+        <v>91692</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759616</v>
+        <v>759568</v>
       </c>
       <c r="R17" t="n">
-        <v>7074094</v>
+        <v>7074103</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2573,12 +2566,12 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Granhögstubbe knäckt</t>
+          <t>Äldre granlåga</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe knäckt</t>
+          <t>Picea abies # Äldre granlåga</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2596,10 +2589,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130261233</v>
+        <v>130261235</v>
       </c>
       <c r="B18" t="n">
-        <v>57985</v>
+        <v>57823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2607,42 +2600,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759425</v>
+        <v>759616</v>
       </c>
       <c r="R18" t="n">
-        <v>7074122</v>
+        <v>7074094</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2672,21 +2662,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2695,6 +2675,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Granhögstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe knäckt</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -2357,53 +2357,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130261233</v>
+        <v>130261224</v>
       </c>
       <c r="B16" t="n">
-        <v>57985</v>
+        <v>91692</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759425</v>
+        <v>759568</v>
       </c>
       <c r="R16" t="n">
-        <v>7074122</v>
+        <v>7074103</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2433,21 +2425,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2456,6 +2438,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Äldre granlåga</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre granlåga</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2472,45 +2474,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130261224</v>
+        <v>130261235</v>
       </c>
       <c r="B17" t="n">
-        <v>91692</v>
+        <v>57823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759568</v>
+        <v>759616</v>
       </c>
       <c r="R17" t="n">
-        <v>7074103</v>
+        <v>7074094</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2566,12 +2573,12 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Äldre granlåga</t>
+          <t>Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre granlåga</t>
+          <t>Picea abies # Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2589,10 +2596,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130261235</v>
+        <v>130261233</v>
       </c>
       <c r="B18" t="n">
-        <v>57823</v>
+        <v>57985</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2600,39 +2607,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759616</v>
+        <v>759425</v>
       </c>
       <c r="R18" t="n">
-        <v>7074094</v>
+        <v>7074122</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2662,11 +2672,21 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2675,26 +2695,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Granhögstubbe knäckt</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe knäckt</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -1292,7 +1292,7 @@
         <v>130261223</v>
       </c>
       <c r="B7" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>130261227</v>
       </c>
       <c r="B9" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130261249</v>
+        <v>130261225</v>
       </c>
       <c r="B12" t="n">
-        <v>58198</v>
+        <v>91695</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1897,42 +1897,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759466</v>
+        <v>759453</v>
       </c>
       <c r="R12" t="n">
-        <v>7074152</v>
+        <v>7074313</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1962,21 +1954,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1985,6 +1967,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Tunnare granlåga invid äldre talltorraka</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies # Tunnare granlåga invid äldre talltorraka</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2001,10 +2003,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130261225</v>
+        <v>130261249</v>
       </c>
       <c r="B13" t="n">
-        <v>91692</v>
+        <v>58198</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2012,34 +2014,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759453</v>
+        <v>759466</v>
       </c>
       <c r="R13" t="n">
-        <v>7074313</v>
+        <v>7074152</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2069,11 +2079,21 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2082,26 +2102,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Tunnare granlåga invid äldre talltorraka</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies # Tunnare granlåga invid äldre talltorraka</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2121,7 +2121,7 @@
         <v>130261254</v>
       </c>
       <c r="B14" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>130261257</v>
       </c>
       <c r="B15" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,45 +2357,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130261224</v>
+        <v>130261235</v>
       </c>
       <c r="B16" t="n">
-        <v>91692</v>
+        <v>57823</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759568</v>
+        <v>759616</v>
       </c>
       <c r="R16" t="n">
-        <v>7074103</v>
+        <v>7074094</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2451,12 +2456,12 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Äldre granlåga</t>
+          <t>Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre granlåga</t>
+          <t>Picea abies # Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2474,50 +2479,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130261235</v>
+        <v>130261224</v>
       </c>
       <c r="B17" t="n">
-        <v>57823</v>
+        <v>91695</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759616</v>
+        <v>759568</v>
       </c>
       <c r="R17" t="n">
-        <v>7074094</v>
+        <v>7074103</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Granhögstubbe knäckt</t>
+          <t>Äldre granlåga</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe knäckt</t>
+          <t>Picea abies # Äldre granlåga</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2714,7 +2714,7 @@
         <v>130261256</v>
       </c>
       <c r="B19" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2950,50 +2950,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130261242</v>
+        <v>130261226</v>
       </c>
       <c r="B21" t="n">
-        <v>57823</v>
+        <v>91695</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759521</v>
+        <v>759410</v>
       </c>
       <c r="R21" t="n">
-        <v>7074133</v>
+        <v>7074242</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3028,11 +3023,6 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Vid basen</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3054,12 +3044,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Knäckt gran</t>
+          <t>Granlåga rotknäckt</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Knäckt gran</t>
+          <t>Picea abies # Granlåga rotknäckt</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3077,7 +3067,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130261237</v>
+        <v>130261242</v>
       </c>
       <c r="B22" t="n">
         <v>57823</v>
@@ -3117,10 +3107,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759528</v>
+        <v>759521</v>
       </c>
       <c r="R22" t="n">
-        <v>7074150</v>
+        <v>7074133</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3157,7 +3147,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Högt upp</t>
+          <t>Vid basen</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3181,12 +3171,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Knäckt gran</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Knäckt gran</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3204,10 +3194,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130261231</v>
+        <v>130261237</v>
       </c>
       <c r="B23" t="n">
-        <v>57826</v>
+        <v>57823</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3215,16 +3205,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3244,10 +3234,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759348</v>
+        <v>759528</v>
       </c>
       <c r="R23" t="n">
-        <v>7074185</v>
+        <v>7074150</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3284,7 +3274,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på granlåga</t>
+          <t>Högt upp</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3308,12 +3298,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3331,45 +3321,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130261226</v>
+        <v>130261243</v>
       </c>
       <c r="B24" t="n">
-        <v>91692</v>
+        <v>57823</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759410</v>
+        <v>759457</v>
       </c>
       <c r="R24" t="n">
-        <v>7074242</v>
+        <v>7074149</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3404,6 +3399,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Kåda</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3423,14 +3423,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>Granlåga rotknäckt</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga rotknäckt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3448,10 +3443,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130261243</v>
+        <v>130261231</v>
       </c>
       <c r="B25" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,16 +3454,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3479,7 +3474,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3488,10 +3483,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759457</v>
+        <v>759348</v>
       </c>
       <c r="R25" t="n">
-        <v>7074149</v>
+        <v>7074185</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3528,7 +3523,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Kåda</t>
+          <t>Ringhack på granlåga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3550,9 +3545,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3573,7 +3573,7 @@
         <v>130261255</v>
       </c>
       <c r="B26" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>130261258</v>
       </c>
       <c r="B27" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>130261259</v>
       </c>
       <c r="B28" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -1292,7 +1292,7 @@
         <v>130261223</v>
       </c>
       <c r="B7" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>130261234</v>
       </c>
       <c r="B8" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>130261227</v>
       </c>
       <c r="B9" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>130261236</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1764,50 +1764,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130261241</v>
+        <v>130261225</v>
       </c>
       <c r="B11" t="n">
-        <v>57823</v>
+        <v>91721</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759358</v>
+        <v>759453</v>
       </c>
       <c r="R11" t="n">
-        <v>7074193</v>
+        <v>7074313</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1863,12 +1858,12 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt</t>
+          <t>Tunnare granlåga invid äldre talltorraka</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies # Tunnare granlåga invid äldre talltorraka</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1886,45 +1881,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130261225</v>
+        <v>130261241</v>
       </c>
       <c r="B12" t="n">
-        <v>91695</v>
+        <v>57849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759453</v>
+        <v>759358</v>
       </c>
       <c r="R12" t="n">
-        <v>7074313</v>
+        <v>7074193</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>Tunnare granlåga invid äldre talltorraka</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies # Tunnare granlåga invid äldre talltorraka</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2006,7 +2006,7 @@
         <v>130261249</v>
       </c>
       <c r="B13" t="n">
-        <v>58198</v>
+        <v>58224</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>130261254</v>
       </c>
       <c r="B14" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>130261257</v>
       </c>
       <c r="B15" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>130261235</v>
       </c>
       <c r="B16" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>130261224</v>
       </c>
       <c r="B17" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>130261233</v>
       </c>
       <c r="B18" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>130261256</v>
       </c>
       <c r="B19" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>130261239</v>
       </c>
       <c r="B20" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>130261226</v>
       </c>
       <c r="B21" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         <v>130261242</v>
       </c>
       <c r="B22" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>130261237</v>
       </c>
       <c r="B23" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>130261243</v>
       </c>
       <c r="B24" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>130261231</v>
       </c>
       <c r="B25" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3570,10 +3570,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130261255</v>
+        <v>130261258</v>
       </c>
       <c r="B26" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759576</v>
+        <v>759498</v>
       </c>
       <c r="R26" t="n">
-        <v>7074103</v>
+        <v>7074364</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3664,12 +3664,12 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Granstubbe knäckt</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe knäckt</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130261258</v>
+        <v>130261255</v>
       </c>
       <c r="B27" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759498</v>
+        <v>759576</v>
       </c>
       <c r="R27" t="n">
-        <v>7074364</v>
+        <v>7074103</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Picea abies # Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3807,7 +3807,7 @@
         <v>130261259</v>
       </c>
       <c r="B28" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>130261240</v>
       </c>
       <c r="B29" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>130261228</v>
       </c>
       <c r="B30" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>130261238</v>
       </c>
       <c r="B31" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -3804,10 +3804,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130261259</v>
+        <v>130261240</v>
       </c>
       <c r="B28" t="n">
-        <v>91753</v>
+        <v>57849</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,34 +3815,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>759622</v>
+        <v>759411</v>
       </c>
       <c r="R28" t="n">
-        <v>7074145</v>
+        <v>7074135</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3898,12 +3903,12 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3921,10 +3926,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130261240</v>
+        <v>130261259</v>
       </c>
       <c r="B29" t="n">
-        <v>57849</v>
+        <v>91753</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3932,39 +3937,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759411</v>
+        <v>759622</v>
       </c>
       <c r="R29" t="n">
-        <v>7074135</v>
+        <v>7074145</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4020,12 +4020,12 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -1292,7 +1292,7 @@
         <v>130261223</v>
       </c>
       <c r="B7" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>130261227</v>
       </c>
       <c r="B9" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>130261225</v>
       </c>
       <c r="B11" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>130261254</v>
       </c>
       <c r="B14" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>130261257</v>
       </c>
       <c r="B15" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>130261224</v>
       </c>
       <c r="B17" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>130261256</v>
       </c>
       <c r="B19" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>130261226</v>
       </c>
       <c r="B21" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3321,10 +3321,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130261243</v>
+        <v>130261231</v>
       </c>
       <c r="B24" t="n">
-        <v>57849</v>
+        <v>57852</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3332,16 +3332,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3352,7 +3352,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759457</v>
+        <v>759348</v>
       </c>
       <c r="R24" t="n">
-        <v>7074149</v>
+        <v>7074185</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Kåda</t>
+          <t>Ringhack på granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3423,9 +3423,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3443,10 +3448,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130261231</v>
+        <v>130261243</v>
       </c>
       <c r="B25" t="n">
-        <v>57852</v>
+        <v>57849</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3454,16 +3459,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3474,7 +3479,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3483,10 +3488,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759348</v>
+        <v>759457</v>
       </c>
       <c r="R25" t="n">
-        <v>7074185</v>
+        <v>7074149</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3523,7 +3528,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack på granlåga</t>
+          <t>Kåda</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3545,14 +3550,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3570,10 +3570,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130261258</v>
+        <v>130261255</v>
       </c>
       <c r="B26" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759498</v>
+        <v>759576</v>
       </c>
       <c r="R26" t="n">
-        <v>7074364</v>
+        <v>7074103</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3664,12 +3664,12 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Picea abies # Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130261255</v>
+        <v>130261258</v>
       </c>
       <c r="B27" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759576</v>
+        <v>759498</v>
       </c>
       <c r="R27" t="n">
-        <v>7074103</v>
+        <v>7074364</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>Granstubbe knäckt</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe knäckt</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3804,10 +3804,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130261240</v>
+        <v>130261259</v>
       </c>
       <c r="B28" t="n">
-        <v>57849</v>
+        <v>91754</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,39 +3815,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>759411</v>
+        <v>759622</v>
       </c>
       <c r="R28" t="n">
-        <v>7074135</v>
+        <v>7074145</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3903,12 +3898,12 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3926,10 +3921,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130261259</v>
+        <v>130261240</v>
       </c>
       <c r="B29" t="n">
-        <v>91753</v>
+        <v>57849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3937,34 +3932,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759622</v>
+        <v>759411</v>
       </c>
       <c r="R29" t="n">
-        <v>7074145</v>
+        <v>7074135</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4020,12 +4020,12 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -1292,7 +1292,7 @@
         <v>130261223</v>
       </c>
       <c r="B7" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>130261227</v>
       </c>
       <c r="B9" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1764,45 +1764,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130261225</v>
+        <v>130261241</v>
       </c>
       <c r="B11" t="n">
-        <v>91722</v>
+        <v>57849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759453</v>
+        <v>759358</v>
       </c>
       <c r="R11" t="n">
-        <v>7074313</v>
+        <v>7074193</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1858,12 +1863,12 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>Tunnare granlåga invid äldre talltorraka</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies # Tunnare granlåga invid äldre talltorraka</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1881,27 +1886,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130261241</v>
+        <v>130261249</v>
       </c>
       <c r="B12" t="n">
-        <v>57849</v>
+        <v>58224</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1910,21 +1915,24 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759358</v>
+        <v>759466</v>
       </c>
       <c r="R12" t="n">
-        <v>7074193</v>
+        <v>7074152</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1954,11 +1962,21 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1967,26 +1985,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Granlåga, knäckt</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga, knäckt</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2003,10 +2001,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130261249</v>
+        <v>130261225</v>
       </c>
       <c r="B13" t="n">
-        <v>58224</v>
+        <v>91723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2014,42 +2012,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759466</v>
+        <v>759453</v>
       </c>
       <c r="R13" t="n">
-        <v>7074152</v>
+        <v>7074313</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2079,21 +2069,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2102,6 +2082,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Tunnare granlåga invid äldre talltorraka</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies # Tunnare granlåga invid äldre talltorraka</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2121,7 +2121,7 @@
         <v>130261254</v>
       </c>
       <c r="B14" t="n">
-        <v>91754</v>
+        <v>91755</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>130261257</v>
       </c>
       <c r="B15" t="n">
-        <v>91754</v>
+        <v>91755</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,50 +2357,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130261235</v>
+        <v>130261224</v>
       </c>
       <c r="B16" t="n">
-        <v>57849</v>
+        <v>91723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759616</v>
+        <v>759568</v>
       </c>
       <c r="R16" t="n">
-        <v>7074094</v>
+        <v>7074103</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2456,12 +2451,12 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Granhögstubbe knäckt</t>
+          <t>Äldre granlåga</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe knäckt</t>
+          <t>Picea abies # Äldre granlåga</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2479,45 +2474,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130261224</v>
+        <v>130261235</v>
       </c>
       <c r="B17" t="n">
-        <v>91722</v>
+        <v>57849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759568</v>
+        <v>759616</v>
       </c>
       <c r="R17" t="n">
-        <v>7074103</v>
+        <v>7074094</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Äldre granlåga</t>
+          <t>Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre granlåga</t>
+          <t>Picea abies # Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2714,7 +2714,7 @@
         <v>130261256</v>
       </c>
       <c r="B19" t="n">
-        <v>91754</v>
+        <v>91755</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2950,45 +2950,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130261226</v>
+        <v>130261242</v>
       </c>
       <c r="B21" t="n">
-        <v>91722</v>
+        <v>57849</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759410</v>
+        <v>759521</v>
       </c>
       <c r="R21" t="n">
-        <v>7074242</v>
+        <v>7074133</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3023,6 +3028,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3044,12 +3054,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Granlåga rotknäckt</t>
+          <t>Knäckt gran</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga rotknäckt</t>
+          <t>Picea abies # Knäckt gran</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3067,7 +3077,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130261242</v>
+        <v>130261237</v>
       </c>
       <c r="B22" t="n">
         <v>57849</v>
@@ -3107,10 +3117,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759521</v>
+        <v>759528</v>
       </c>
       <c r="R22" t="n">
-        <v>7074133</v>
+        <v>7074150</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3147,7 +3157,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Vid basen</t>
+          <t>Högt upp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3171,12 +3181,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Knäckt gran</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Knäckt gran</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3194,7 +3204,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130261237</v>
+        <v>130261243</v>
       </c>
       <c r="B23" t="n">
         <v>57849</v>
@@ -3225,7 +3235,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3234,10 +3244,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759528</v>
+        <v>759457</v>
       </c>
       <c r="R23" t="n">
-        <v>7074150</v>
+        <v>7074149</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3274,7 +3284,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Högt upp</t>
+          <t>Kåda</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3296,14 +3306,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3321,50 +3326,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130261231</v>
+        <v>130261226</v>
       </c>
       <c r="B24" t="n">
-        <v>57852</v>
+        <v>91723</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759348</v>
+        <v>759410</v>
       </c>
       <c r="R24" t="n">
-        <v>7074185</v>
+        <v>7074242</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3399,11 +3399,6 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på granlåga</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3425,12 +3420,12 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga rotknäckt</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlåga rotknäckt</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3448,10 +3443,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130261243</v>
+        <v>130261231</v>
       </c>
       <c r="B25" t="n">
-        <v>57849</v>
+        <v>57852</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,16 +3454,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3479,7 +3474,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3488,10 +3483,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759457</v>
+        <v>759348</v>
       </c>
       <c r="R25" t="n">
-        <v>7074149</v>
+        <v>7074185</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3528,7 +3523,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Kåda</t>
+          <t>Ringhack på granlåga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3550,9 +3545,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3570,10 +3570,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130261255</v>
+        <v>130261258</v>
       </c>
       <c r="B26" t="n">
-        <v>91754</v>
+        <v>91755</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759576</v>
+        <v>759498</v>
       </c>
       <c r="R26" t="n">
-        <v>7074103</v>
+        <v>7074364</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3664,12 +3664,12 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Granstubbe knäckt</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe knäckt</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130261258</v>
+        <v>130261255</v>
       </c>
       <c r="B27" t="n">
-        <v>91754</v>
+        <v>91755</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759498</v>
+        <v>759576</v>
       </c>
       <c r="R27" t="n">
-        <v>7074364</v>
+        <v>7074103</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Picea abies # Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3807,7 +3807,7 @@
         <v>130261259</v>
       </c>
       <c r="B28" t="n">
-        <v>91754</v>
+        <v>91755</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -1292,7 +1292,7 @@
         <v>130261223</v>
       </c>
       <c r="B7" t="n">
-        <v>91723</v>
+        <v>91725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>130261234</v>
       </c>
       <c r="B8" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>130261227</v>
       </c>
       <c r="B9" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>130261236</v>
       </c>
       <c r="B10" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1764,27 +1764,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130261241</v>
+        <v>130261249</v>
       </c>
       <c r="B11" t="n">
-        <v>57849</v>
+        <v>58226</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1793,21 +1793,24 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759358</v>
+        <v>759466</v>
       </c>
       <c r="R11" t="n">
-        <v>7074193</v>
+        <v>7074152</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1837,11 +1840,21 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1850,26 +1863,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Granlåga, knäckt</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga, knäckt</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1886,10 +1879,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130261249</v>
+        <v>130261225</v>
       </c>
       <c r="B12" t="n">
-        <v>58224</v>
+        <v>91725</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1897,42 +1890,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759466</v>
+        <v>759453</v>
       </c>
       <c r="R12" t="n">
-        <v>7074152</v>
+        <v>7074313</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1962,21 +1947,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1985,6 +1960,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Tunnare granlåga invid äldre talltorraka</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies # Tunnare granlåga invid äldre talltorraka</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2001,45 +1996,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130261225</v>
+        <v>130261241</v>
       </c>
       <c r="B13" t="n">
-        <v>91723</v>
+        <v>57851</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759453</v>
+        <v>759358</v>
       </c>
       <c r="R13" t="n">
-        <v>7074313</v>
+        <v>7074193</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>Tunnare granlåga invid äldre talltorraka</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies # Tunnare granlåga invid äldre talltorraka</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2121,7 +2121,7 @@
         <v>130261254</v>
       </c>
       <c r="B14" t="n">
-        <v>91755</v>
+        <v>91757</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>130261257</v>
       </c>
       <c r="B15" t="n">
-        <v>91755</v>
+        <v>91757</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,45 +2357,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130261224</v>
+        <v>130261235</v>
       </c>
       <c r="B16" t="n">
-        <v>91723</v>
+        <v>57851</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759568</v>
+        <v>759616</v>
       </c>
       <c r="R16" t="n">
-        <v>7074103</v>
+        <v>7074094</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2451,12 +2456,12 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Äldre granlåga</t>
+          <t>Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre granlåga</t>
+          <t>Picea abies # Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2474,50 +2479,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130261235</v>
+        <v>130261224</v>
       </c>
       <c r="B17" t="n">
-        <v>57849</v>
+        <v>91725</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759616</v>
+        <v>759568</v>
       </c>
       <c r="R17" t="n">
-        <v>7074094</v>
+        <v>7074103</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Granhögstubbe knäckt</t>
+          <t>Äldre granlåga</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe knäckt</t>
+          <t>Picea abies # Äldre granlåga</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2599,7 +2599,7 @@
         <v>130261233</v>
       </c>
       <c r="B18" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>130261256</v>
       </c>
       <c r="B19" t="n">
-        <v>91755</v>
+        <v>91757</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>130261239</v>
       </c>
       <c r="B20" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2950,10 +2950,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130261242</v>
+        <v>130261231</v>
       </c>
       <c r="B21" t="n">
-        <v>57849</v>
+        <v>57854</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2961,16 +2961,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2990,10 +2990,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759521</v>
+        <v>759348</v>
       </c>
       <c r="R21" t="n">
-        <v>7074133</v>
+        <v>7074185</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Vid basen</t>
+          <t>Ringhack på granlåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Knäckt gran</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Knäckt gran</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3077,50 +3077,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130261237</v>
+        <v>130261226</v>
       </c>
       <c r="B22" t="n">
-        <v>57849</v>
+        <v>91725</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759528</v>
+        <v>759410</v>
       </c>
       <c r="R22" t="n">
-        <v>7074150</v>
+        <v>7074242</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3155,11 +3150,6 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Högt upp</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3181,12 +3171,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granlåga rotknäckt</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granlåga rotknäckt</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3204,10 +3194,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130261243</v>
+        <v>130261242</v>
       </c>
       <c r="B23" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,7 +3225,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3244,10 +3234,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759457</v>
+        <v>759521</v>
       </c>
       <c r="R23" t="n">
-        <v>7074149</v>
+        <v>7074133</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3284,7 +3274,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Kåda</t>
+          <t>Vid basen</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3306,9 +3296,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Knäckt gran</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Knäckt gran</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3326,45 +3321,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130261226</v>
+        <v>130261237</v>
       </c>
       <c r="B24" t="n">
-        <v>91723</v>
+        <v>57851</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759410</v>
+        <v>759528</v>
       </c>
       <c r="R24" t="n">
-        <v>7074242</v>
+        <v>7074150</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3399,6 +3399,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Högt upp</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3420,12 +3425,12 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Granlåga rotknäckt</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga rotknäckt</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3443,10 +3448,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130261231</v>
+        <v>130261243</v>
       </c>
       <c r="B25" t="n">
-        <v>57852</v>
+        <v>57851</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3454,16 +3459,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3474,7 +3479,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3483,10 +3488,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759348</v>
+        <v>759457</v>
       </c>
       <c r="R25" t="n">
-        <v>7074185</v>
+        <v>7074149</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3523,7 +3528,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack på granlåga</t>
+          <t>Kåda</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3545,14 +3550,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3570,10 +3570,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130261258</v>
+        <v>130261255</v>
       </c>
       <c r="B26" t="n">
-        <v>91755</v>
+        <v>91757</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759498</v>
+        <v>759576</v>
       </c>
       <c r="R26" t="n">
-        <v>7074364</v>
+        <v>7074103</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3664,12 +3664,12 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Picea abies # Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130261255</v>
+        <v>130261258</v>
       </c>
       <c r="B27" t="n">
-        <v>91755</v>
+        <v>91757</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759576</v>
+        <v>759498</v>
       </c>
       <c r="R27" t="n">
-        <v>7074103</v>
+        <v>7074364</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>Granstubbe knäckt</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe knäckt</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3804,10 +3804,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130261259</v>
+        <v>130261240</v>
       </c>
       <c r="B28" t="n">
-        <v>91755</v>
+        <v>57851</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,34 +3815,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>759622</v>
+        <v>759411</v>
       </c>
       <c r="R28" t="n">
-        <v>7074145</v>
+        <v>7074135</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3898,12 +3903,12 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3921,10 +3926,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130261240</v>
+        <v>130261259</v>
       </c>
       <c r="B29" t="n">
-        <v>57849</v>
+        <v>91757</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3932,39 +3937,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759411</v>
+        <v>759622</v>
       </c>
       <c r="R29" t="n">
-        <v>7074135</v>
+        <v>7074145</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4020,12 +4020,12 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4046,7 +4046,7 @@
         <v>130261228</v>
       </c>
       <c r="B30" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>130261238</v>
       </c>
       <c r="B31" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -1289,45 +1289,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130261223</v>
+        <v>130261234</v>
       </c>
       <c r="B7" t="n">
-        <v>91725</v>
+        <v>58013</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759450</v>
+        <v>759386</v>
       </c>
       <c r="R7" t="n">
-        <v>7074279</v>
+        <v>7074195</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1357,11 +1369,21 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1370,26 +1392,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1406,57 +1408,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130261234</v>
+        <v>130261223</v>
       </c>
       <c r="B8" t="n">
-        <v>58013</v>
+        <v>91725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759386</v>
+        <v>759450</v>
       </c>
       <c r="R8" t="n">
-        <v>7074195</v>
+        <v>7074279</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1486,21 +1476,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1509,6 +1489,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga knäckt</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -2357,50 +2357,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130261235</v>
+        <v>130261224</v>
       </c>
       <c r="B16" t="n">
-        <v>57851</v>
+        <v>91725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759616</v>
+        <v>759568</v>
       </c>
       <c r="R16" t="n">
-        <v>7074094</v>
+        <v>7074103</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2456,12 +2451,12 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Granhögstubbe knäckt</t>
+          <t>Äldre granlåga</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe knäckt</t>
+          <t>Picea abies # Äldre granlåga</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2479,45 +2474,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130261224</v>
+        <v>130261235</v>
       </c>
       <c r="B17" t="n">
-        <v>91725</v>
+        <v>57851</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759568</v>
+        <v>759616</v>
       </c>
       <c r="R17" t="n">
-        <v>7074103</v>
+        <v>7074094</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Äldre granlåga</t>
+          <t>Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre granlåga</t>
+          <t>Picea abies # Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130261231</v>
+        <v>130261242</v>
       </c>
       <c r="B21" t="n">
-        <v>57854</v>
+        <v>57851</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2961,16 +2961,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2990,10 +2990,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759348</v>
+        <v>759521</v>
       </c>
       <c r="R21" t="n">
-        <v>7074185</v>
+        <v>7074133</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på granlåga</t>
+          <t>Vid basen</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Knäckt gran</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Knäckt gran</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3077,45 +3077,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130261226</v>
+        <v>130261237</v>
       </c>
       <c r="B22" t="n">
-        <v>91725</v>
+        <v>57851</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759410</v>
+        <v>759528</v>
       </c>
       <c r="R22" t="n">
-        <v>7074242</v>
+        <v>7074150</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3150,6 +3155,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Högt upp</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3171,12 +3181,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Granlåga rotknäckt</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga rotknäckt</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3194,7 +3204,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130261242</v>
+        <v>130261243</v>
       </c>
       <c r="B23" t="n">
         <v>57851</v>
@@ -3225,7 +3235,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3234,10 +3244,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759521</v>
+        <v>759457</v>
       </c>
       <c r="R23" t="n">
-        <v>7074133</v>
+        <v>7074149</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3274,7 +3284,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Vid basen</t>
+          <t>Kåda</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3296,14 +3306,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Knäckt gran</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Knäckt gran</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3321,50 +3326,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130261237</v>
+        <v>130261226</v>
       </c>
       <c r="B24" t="n">
-        <v>57851</v>
+        <v>91725</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759528</v>
+        <v>759410</v>
       </c>
       <c r="R24" t="n">
-        <v>7074150</v>
+        <v>7074242</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3399,11 +3399,6 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Högt upp</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3425,12 +3420,12 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granlåga rotknäckt</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granlåga rotknäckt</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3448,10 +3443,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130261243</v>
+        <v>130261231</v>
       </c>
       <c r="B25" t="n">
-        <v>57851</v>
+        <v>57854</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3459,16 +3454,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3479,7 +3474,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3488,10 +3483,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759457</v>
+        <v>759348</v>
       </c>
       <c r="R25" t="n">
-        <v>7074149</v>
+        <v>7074185</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3528,7 +3523,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Kåda</t>
+          <t>Ringhack på granlåga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3550,9 +3545,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3570,7 +3570,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130261255</v>
+        <v>130261258</v>
       </c>
       <c r="B26" t="n">
         <v>91757</v>
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759576</v>
+        <v>759498</v>
       </c>
       <c r="R26" t="n">
-        <v>7074103</v>
+        <v>7074364</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3664,12 +3664,12 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Granstubbe knäckt</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe knäckt</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3687,7 +3687,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130261258</v>
+        <v>130261255</v>
       </c>
       <c r="B27" t="n">
         <v>91757</v>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759498</v>
+        <v>759576</v>
       </c>
       <c r="R27" t="n">
-        <v>7074364</v>
+        <v>7074103</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Picea abies # Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3804,10 +3804,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130261240</v>
+        <v>130261259</v>
       </c>
       <c r="B28" t="n">
-        <v>57851</v>
+        <v>91757</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3815,39 +3815,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>759411</v>
+        <v>759622</v>
       </c>
       <c r="R28" t="n">
-        <v>7074135</v>
+        <v>7074145</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3903,12 +3898,12 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3926,10 +3921,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130261259</v>
+        <v>130261240</v>
       </c>
       <c r="B29" t="n">
-        <v>91757</v>
+        <v>57851</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3937,34 +3932,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759622</v>
+        <v>759411</v>
       </c>
       <c r="R29" t="n">
-        <v>7074145</v>
+        <v>7074135</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4020,12 +4020,12 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -1764,10 +1764,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130261249</v>
+        <v>130261225</v>
       </c>
       <c r="B11" t="n">
-        <v>58226</v>
+        <v>91725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,42 +1775,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759466</v>
+        <v>759453</v>
       </c>
       <c r="R11" t="n">
-        <v>7074152</v>
+        <v>7074313</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1840,21 +1832,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1863,6 +1845,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Tunnare granlåga invid äldre talltorraka</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies # Tunnare granlåga invid äldre talltorraka</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1879,10 +1881,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130261225</v>
+        <v>130261249</v>
       </c>
       <c r="B12" t="n">
-        <v>91725</v>
+        <v>58226</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,34 +1892,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759453</v>
+        <v>759466</v>
       </c>
       <c r="R12" t="n">
-        <v>7074313</v>
+        <v>7074152</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1947,11 +1957,21 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1960,26 +1980,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Tunnare granlåga invid äldre talltorraka</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies # Tunnare granlåga invid äldre talltorraka</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2357,45 +2357,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130261224</v>
+        <v>130261233</v>
       </c>
       <c r="B16" t="n">
-        <v>91725</v>
+        <v>58013</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759568</v>
+        <v>759425</v>
       </c>
       <c r="R16" t="n">
-        <v>7074103</v>
+        <v>7074122</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2425,11 +2433,21 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2438,26 +2456,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Äldre granlåga</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre granlåga</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2596,53 +2594,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130261233</v>
+        <v>130261224</v>
       </c>
       <c r="B18" t="n">
-        <v>58013</v>
+        <v>91725</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759425</v>
+        <v>759568</v>
       </c>
       <c r="R18" t="n">
-        <v>7074122</v>
+        <v>7074103</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2672,21 +2662,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2695,6 +2675,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Äldre granlåga</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre granlåga</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2950,50 +2950,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130261242</v>
+        <v>130261226</v>
       </c>
       <c r="B21" t="n">
-        <v>57851</v>
+        <v>91725</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759521</v>
+        <v>759410</v>
       </c>
       <c r="R21" t="n">
-        <v>7074133</v>
+        <v>7074242</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3028,11 +3023,6 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Vid basen</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3054,12 +3044,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Knäckt gran</t>
+          <t>Granlåga rotknäckt</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Knäckt gran</t>
+          <t>Picea abies # Granlåga rotknäckt</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3077,7 +3067,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130261237</v>
+        <v>130261242</v>
       </c>
       <c r="B22" t="n">
         <v>57851</v>
@@ -3117,10 +3107,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759528</v>
+        <v>759521</v>
       </c>
       <c r="R22" t="n">
-        <v>7074150</v>
+        <v>7074133</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3157,7 +3147,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Högt upp</t>
+          <t>Vid basen</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3181,12 +3171,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Knäckt gran</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Knäckt gran</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3204,7 +3194,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130261243</v>
+        <v>130261237</v>
       </c>
       <c r="B23" t="n">
         <v>57851</v>
@@ -3235,7 +3225,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3244,10 +3234,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759457</v>
+        <v>759528</v>
       </c>
       <c r="R23" t="n">
-        <v>7074149</v>
+        <v>7074150</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3284,7 +3274,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Kåda</t>
+          <t>Högt upp</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3306,9 +3296,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3326,45 +3321,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130261226</v>
+        <v>130261243</v>
       </c>
       <c r="B24" t="n">
-        <v>91725</v>
+        <v>57851</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759410</v>
+        <v>759457</v>
       </c>
       <c r="R24" t="n">
-        <v>7074242</v>
+        <v>7074149</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3399,6 +3399,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Kåda</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3418,14 +3423,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>Granlåga rotknäckt</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga rotknäckt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3570,7 +3570,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130261258</v>
+        <v>130261255</v>
       </c>
       <c r="B26" t="n">
         <v>91757</v>
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759498</v>
+        <v>759576</v>
       </c>
       <c r="R26" t="n">
-        <v>7074364</v>
+        <v>7074103</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3664,12 +3664,12 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Picea abies # Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3687,7 +3687,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130261255</v>
+        <v>130261258</v>
       </c>
       <c r="B27" t="n">
         <v>91757</v>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759576</v>
+        <v>759498</v>
       </c>
       <c r="R27" t="n">
-        <v>7074103</v>
+        <v>7074364</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>Granstubbe knäckt</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe knäckt</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -1289,57 +1289,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130261234</v>
+        <v>130261223</v>
       </c>
       <c r="B7" t="n">
-        <v>58013</v>
+        <v>91725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759386</v>
+        <v>759450</v>
       </c>
       <c r="R7" t="n">
-        <v>7074195</v>
+        <v>7074279</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1369,21 +1357,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1392,6 +1370,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga knäckt</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1408,45 +1406,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130261223</v>
+        <v>130261234</v>
       </c>
       <c r="B8" t="n">
-        <v>91725</v>
+        <v>58013</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759450</v>
+        <v>759386</v>
       </c>
       <c r="R8" t="n">
-        <v>7074279</v>
+        <v>7074195</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1476,11 +1486,21 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1489,26 +1509,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1881,27 +1881,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130261249</v>
+        <v>130261241</v>
       </c>
       <c r="B12" t="n">
-        <v>58226</v>
+        <v>57851</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1910,24 +1910,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759466</v>
+        <v>759358</v>
       </c>
       <c r="R12" t="n">
-        <v>7074152</v>
+        <v>7074193</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1957,21 +1954,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1980,6 +1967,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Granlåga, knäckt</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga, knäckt</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1996,27 +2003,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130261241</v>
+        <v>130261249</v>
       </c>
       <c r="B13" t="n">
-        <v>57851</v>
+        <v>58226</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2025,21 +2032,24 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759358</v>
+        <v>759466</v>
       </c>
       <c r="R13" t="n">
-        <v>7074193</v>
+        <v>7074152</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2069,11 +2079,21 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2082,26 +2102,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Granlåga, knäckt</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga, knäckt</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2357,53 +2357,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130261233</v>
+        <v>130261224</v>
       </c>
       <c r="B16" t="n">
-        <v>58013</v>
+        <v>91725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759425</v>
+        <v>759568</v>
       </c>
       <c r="R16" t="n">
-        <v>7074122</v>
+        <v>7074103</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2433,21 +2425,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2456,6 +2438,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Äldre granlåga</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre granlåga</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2594,45 +2596,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130261224</v>
+        <v>130261233</v>
       </c>
       <c r="B18" t="n">
-        <v>91725</v>
+        <v>58013</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759568</v>
+        <v>759425</v>
       </c>
       <c r="R18" t="n">
-        <v>7074103</v>
+        <v>7074122</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2662,11 +2672,21 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2675,26 +2695,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Äldre granlåga</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre granlåga</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2950,45 +2950,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130261226</v>
+        <v>130261242</v>
       </c>
       <c r="B21" t="n">
-        <v>91725</v>
+        <v>57851</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759410</v>
+        <v>759521</v>
       </c>
       <c r="R21" t="n">
-        <v>7074242</v>
+        <v>7074133</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3023,6 +3028,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3044,12 +3054,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Granlåga rotknäckt</t>
+          <t>Knäckt gran</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga rotknäckt</t>
+          <t>Picea abies # Knäckt gran</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3067,7 +3077,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130261242</v>
+        <v>130261237</v>
       </c>
       <c r="B22" t="n">
         <v>57851</v>
@@ -3107,10 +3117,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759521</v>
+        <v>759528</v>
       </c>
       <c r="R22" t="n">
-        <v>7074133</v>
+        <v>7074150</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3147,7 +3157,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Vid basen</t>
+          <t>Högt upp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3171,12 +3181,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Knäckt gran</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Knäckt gran</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3194,7 +3204,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130261237</v>
+        <v>130261243</v>
       </c>
       <c r="B23" t="n">
         <v>57851</v>
@@ -3225,7 +3235,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3234,10 +3244,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759528</v>
+        <v>759457</v>
       </c>
       <c r="R23" t="n">
-        <v>7074150</v>
+        <v>7074149</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3274,7 +3284,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Högt upp</t>
+          <t>Kåda</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3296,14 +3306,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3321,50 +3326,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130261243</v>
+        <v>130261226</v>
       </c>
       <c r="B24" t="n">
-        <v>57851</v>
+        <v>91725</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759457</v>
+        <v>759410</v>
       </c>
       <c r="R24" t="n">
-        <v>7074149</v>
+        <v>7074242</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3399,11 +3399,6 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Kåda</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3423,9 +3418,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Granlåga rotknäckt</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga rotknäckt</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -1764,10 +1764,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130261225</v>
+        <v>130261249</v>
       </c>
       <c r="B11" t="n">
-        <v>91725</v>
+        <v>58226</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,34 +1775,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759453</v>
+        <v>759466</v>
       </c>
       <c r="R11" t="n">
-        <v>7074313</v>
+        <v>7074152</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1832,11 +1840,21 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1845,26 +1863,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Tunnare granlåga invid äldre talltorraka</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies # Tunnare granlåga invid äldre talltorraka</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1881,50 +1879,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130261241</v>
+        <v>130261225</v>
       </c>
       <c r="B12" t="n">
-        <v>57851</v>
+        <v>91725</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759358</v>
+        <v>759453</v>
       </c>
       <c r="R12" t="n">
-        <v>7074193</v>
+        <v>7074313</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1980,12 +1973,12 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt</t>
+          <t>Tunnare granlåga invid äldre talltorraka</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies # Tunnare granlåga invid äldre talltorraka</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2003,27 +1996,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130261249</v>
+        <v>130261241</v>
       </c>
       <c r="B13" t="n">
-        <v>58226</v>
+        <v>57851</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2032,24 +2025,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759466</v>
+        <v>759358</v>
       </c>
       <c r="R13" t="n">
-        <v>7074152</v>
+        <v>7074193</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2079,21 +2069,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2102,6 +2082,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Granlåga, knäckt</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga, knäckt</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2357,45 +2357,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130261224</v>
+        <v>130261233</v>
       </c>
       <c r="B16" t="n">
-        <v>91725</v>
+        <v>58013</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759568</v>
+        <v>759425</v>
       </c>
       <c r="R16" t="n">
-        <v>7074103</v>
+        <v>7074122</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2425,11 +2433,21 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2438,26 +2456,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Äldre granlåga</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre granlåga</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2474,50 +2472,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130261235</v>
+        <v>130261224</v>
       </c>
       <c r="B17" t="n">
-        <v>57851</v>
+        <v>91725</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759616</v>
+        <v>759568</v>
       </c>
       <c r="R17" t="n">
-        <v>7074094</v>
+        <v>7074103</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2573,12 +2566,12 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Granhögstubbe knäckt</t>
+          <t>Äldre granlåga</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe knäckt</t>
+          <t>Picea abies # Äldre granlåga</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2596,10 +2589,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130261233</v>
+        <v>130261235</v>
       </c>
       <c r="B18" t="n">
-        <v>58013</v>
+        <v>57851</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2607,42 +2600,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759425</v>
+        <v>759616</v>
       </c>
       <c r="R18" t="n">
-        <v>7074122</v>
+        <v>7074094</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2672,21 +2662,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2695,6 +2675,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Granhögstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe knäckt</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2950,50 +2950,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130261242</v>
+        <v>130261226</v>
       </c>
       <c r="B21" t="n">
-        <v>57851</v>
+        <v>91725</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759521</v>
+        <v>759410</v>
       </c>
       <c r="R21" t="n">
-        <v>7074133</v>
+        <v>7074242</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3028,11 +3023,6 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Vid basen</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3054,12 +3044,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Knäckt gran</t>
+          <t>Granlåga rotknäckt</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Knäckt gran</t>
+          <t>Picea abies # Granlåga rotknäckt</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3077,7 +3067,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130261237</v>
+        <v>130261242</v>
       </c>
       <c r="B22" t="n">
         <v>57851</v>
@@ -3117,10 +3107,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759528</v>
+        <v>759521</v>
       </c>
       <c r="R22" t="n">
-        <v>7074150</v>
+        <v>7074133</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3157,7 +3147,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Högt upp</t>
+          <t>Vid basen</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3181,12 +3171,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Knäckt gran</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Knäckt gran</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3204,7 +3194,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130261243</v>
+        <v>130261237</v>
       </c>
       <c r="B23" t="n">
         <v>57851</v>
@@ -3235,7 +3225,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3244,10 +3234,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759457</v>
+        <v>759528</v>
       </c>
       <c r="R23" t="n">
-        <v>7074149</v>
+        <v>7074150</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3284,7 +3274,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Kåda</t>
+          <t>Högt upp</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3306,9 +3296,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3326,45 +3321,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130261226</v>
+        <v>130261243</v>
       </c>
       <c r="B24" t="n">
-        <v>91725</v>
+        <v>57851</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759410</v>
+        <v>759457</v>
       </c>
       <c r="R24" t="n">
-        <v>7074242</v>
+        <v>7074149</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3399,6 +3399,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Kåda</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3418,14 +3423,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>Granlåga rotknäckt</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga rotknäckt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -1292,7 +1292,7 @@
         <v>130261223</v>
       </c>
       <c r="B7" t="n">
-        <v>91725</v>
+        <v>91737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>130261234</v>
       </c>
       <c r="B8" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>130261227</v>
       </c>
       <c r="B9" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>130261236</v>
       </c>
       <c r="B10" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>130261249</v>
       </c>
       <c r="B11" t="n">
-        <v>58226</v>
+        <v>58234</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>130261225</v>
       </c>
       <c r="B12" t="n">
-        <v>91725</v>
+        <v>91737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>130261241</v>
       </c>
       <c r="B13" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>130261254</v>
       </c>
       <c r="B14" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>130261257</v>
       </c>
       <c r="B15" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130261233</v>
+        <v>130261235</v>
       </c>
       <c r="B16" t="n">
-        <v>58013</v>
+        <v>57859</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,42 +2368,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759425</v>
+        <v>759616</v>
       </c>
       <c r="R16" t="n">
-        <v>7074122</v>
+        <v>7074094</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2433,21 +2430,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2456,6 +2443,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Granhögstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe knäckt</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2472,45 +2479,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130261224</v>
+        <v>130261233</v>
       </c>
       <c r="B17" t="n">
-        <v>91725</v>
+        <v>58021</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759568</v>
+        <v>759425</v>
       </c>
       <c r="R17" t="n">
-        <v>7074103</v>
+        <v>7074122</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2540,11 +2555,21 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2553,26 +2578,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Äldre granlåga</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre granlåga</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2589,50 +2594,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130261235</v>
+        <v>130261224</v>
       </c>
       <c r="B18" t="n">
-        <v>57851</v>
+        <v>91737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759616</v>
+        <v>759568</v>
       </c>
       <c r="R18" t="n">
-        <v>7074094</v>
+        <v>7074103</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2688,12 +2688,12 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Granhögstubbe knäckt</t>
+          <t>Äldre granlåga</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe knäckt</t>
+          <t>Picea abies # Äldre granlåga</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2714,7 +2714,7 @@
         <v>130261256</v>
       </c>
       <c r="B19" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>130261239</v>
       </c>
       <c r="B20" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2950,45 +2950,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130261226</v>
+        <v>130261242</v>
       </c>
       <c r="B21" t="n">
-        <v>91725</v>
+        <v>57859</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759410</v>
+        <v>759521</v>
       </c>
       <c r="R21" t="n">
-        <v>7074242</v>
+        <v>7074133</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3023,6 +3028,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3044,12 +3054,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Granlåga rotknäckt</t>
+          <t>Knäckt gran</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga rotknäckt</t>
+          <t>Picea abies # Knäckt gran</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3067,10 +3077,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130261242</v>
+        <v>130261237</v>
       </c>
       <c r="B22" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3107,10 +3117,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>759521</v>
+        <v>759528</v>
       </c>
       <c r="R22" t="n">
-        <v>7074133</v>
+        <v>7074150</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3147,7 +3157,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Vid basen</t>
+          <t>Högt upp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3171,12 +3181,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Knäckt gran</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies # Knäckt gran</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3194,10 +3204,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130261237</v>
+        <v>130261243</v>
       </c>
       <c r="B23" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3225,7 +3235,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3234,10 +3244,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759528</v>
+        <v>759457</v>
       </c>
       <c r="R23" t="n">
-        <v>7074150</v>
+        <v>7074149</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3274,7 +3284,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Högt upp</t>
+          <t>Kåda</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3296,14 +3306,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3321,50 +3326,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130261243</v>
+        <v>130261226</v>
       </c>
       <c r="B24" t="n">
-        <v>57851</v>
+        <v>91737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759457</v>
+        <v>759410</v>
       </c>
       <c r="R24" t="n">
-        <v>7074149</v>
+        <v>7074242</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3399,11 +3399,6 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Kåda</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3423,9 +3418,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Granlåga rotknäckt</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga rotknäckt</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3446,7 +3446,7 @@
         <v>130261231</v>
       </c>
       <c r="B25" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>130261255</v>
       </c>
       <c r="B26" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>130261258</v>
       </c>
       <c r="B27" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>130261259</v>
       </c>
       <c r="B28" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>130261240</v>
       </c>
       <c r="B29" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>130261228</v>
       </c>
       <c r="B30" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>130261238</v>
       </c>
       <c r="B31" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>389141</v>
+        <v>144677</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>759504.7830229704</v>
+        <v>759505</v>
       </c>
       <c r="R2" t="n">
-        <v>7074277.174173773</v>
+        <v>7074277</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,24 +743,14 @@
           <t>2011-06-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-06-05</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På samma låga som stjärntagging</t>
+          <t>På samma låga som ullticka</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,6 +770,16 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>Äldre granskog</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Gudrun Norstedt</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>2011005</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,50 +797,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1586002</v>
+        <v>130261254</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Båtsviksberget, 430 m SSV om, Vb</t>
+          <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759504.7830229704</v>
+        <v>759629</v>
       </c>
       <c r="R3" t="n">
-        <v>7074277.174173773</v>
+        <v>7074125</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,22 +862,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-06-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-06-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre fruktkroppar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,40 +884,45 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Äldre granskog</t>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Stående död</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gudrun Norstedt</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gudrun Norstedt</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>389140</v>
+        <v>130261255</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,34 +930,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Båtsviksberget, 430 m SSV om, Vb</t>
+          <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759506.5130177971</v>
+        <v>759576</v>
       </c>
       <c r="R4" t="n">
-        <v>7074272.417682851</v>
+        <v>7074103</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -994,22 +984,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2011-06-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2011-06-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,40 +1001,45 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Äldre granskog</t>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Granstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies # Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gudrun Norstedt</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gudrun Norstedt</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>144677</v>
+        <v>130261256</v>
       </c>
       <c r="B5" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,34 +1047,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Båtsviksberget, 430 m SSV om, Vb</t>
+          <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759504.7830229704</v>
+        <v>759454</v>
       </c>
       <c r="R5" t="n">
-        <v>7074277.174173773</v>
+        <v>7074134</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1116,27 +1101,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2011-06-05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2011-06-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På samma låga som ullticka</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,50 +1118,45 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Äldre granskog</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>Gudrun Norstedt</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>2011005</t>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Granstubbe knäckt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies # Granstubbe knäckt</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gudrun Norstedt</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gudrun Norstedt</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114558886</v>
+        <v>130261257</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,40 +1164,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>300m NO Gröthällberget, Vb</t>
+          <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>759614</v>
+        <v>759449</v>
       </c>
       <c r="R6" t="n">
-        <v>7074148</v>
+        <v>7074314</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1256,12 +1218,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,51 +1232,70 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Stående död</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Andreas Drott</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Andreas Drott, Karl-Henrik  Drott</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130261223</v>
+        <v>130261258</v>
       </c>
       <c r="B7" t="n">
-        <v>91737</v>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1324,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759450</v>
+        <v>759498</v>
       </c>
       <c r="R7" t="n">
-        <v>7074279</v>
+        <v>7074364</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1383,12 +1364,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Granlåga knäckt</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1406,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130261234</v>
+        <v>130261259</v>
       </c>
       <c r="B8" t="n">
-        <v>58021</v>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,46 +1398,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759386</v>
+        <v>759622</v>
       </c>
       <c r="R8" t="n">
-        <v>7074195</v>
+        <v>7074145</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1486,21 +1455,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1509,6 +1468,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Stående död</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1525,10 +1504,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130261227</v>
+        <v>389140</v>
       </c>
       <c r="B9" t="n">
-        <v>91774</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,14 +1535,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Båtsviksberget, 430 m SSV om, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759410</v>
+        <v>759507</v>
       </c>
       <c r="R9" t="n">
-        <v>7074242</v>
+        <v>7074272</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1590,12 +1569,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2011-06-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2011-06-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,45 +1586,35 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Granlåga rotknäckt</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga rotknäckt</t>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre granskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Gudrun Norstedt</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Gudrun Norstedt</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130261236</v>
+        <v>389141</v>
       </c>
       <c r="B10" t="n">
-        <v>57859</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,39 +1622,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Båtsviksberget, 430 m SSV om, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759588</v>
+        <v>759505</v>
       </c>
       <c r="R10" t="n">
-        <v>7074157</v>
+        <v>7074277</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1712,12 +1676,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2011-06-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2011-06-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På samma låga som stjärntagging</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,88 +1698,70 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Granhögstubbe grov, knäckt</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe grov, knäckt</t>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre granskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Gudrun Norstedt</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Gudrun Norstedt</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130261249</v>
+        <v>130261227</v>
       </c>
       <c r="B11" t="n">
-        <v>58234</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>759466</v>
+        <v>759410</v>
       </c>
       <c r="R11" t="n">
-        <v>7074152</v>
+        <v>7074242</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1840,21 +1791,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1863,6 +1804,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Granlåga rotknäckt</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga rotknäckt</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1879,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130261225</v>
+        <v>130261232</v>
       </c>
       <c r="B12" t="n">
-        <v>91737</v>
+        <v>92632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,21 +1851,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1914,10 +1875,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>759453</v>
+        <v>759330</v>
       </c>
       <c r="R12" t="n">
-        <v>7074313</v>
+        <v>7074184</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1973,12 +1934,12 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>Tunnare granlåga invid äldre talltorraka</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies # Tunnare granlåga invid äldre talltorraka</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1996,50 +1957,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130261241</v>
+        <v>1586002</v>
       </c>
       <c r="B13" t="n">
-        <v>57859</v>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Båtsviksberget, 430 m SSV om, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>759358</v>
+        <v>759505</v>
       </c>
       <c r="R13" t="n">
-        <v>7074193</v>
+        <v>7074277</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2066,12 +2022,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2011-06-05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2011-06-05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2083,83 +2039,73 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Granlåga, knäckt</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre granskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Gudrun Norstedt</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Gudrun Norstedt</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130261254</v>
+        <v>122748168</v>
       </c>
       <c r="B14" t="n">
-        <v>91770</v>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>Jenberget NÖ, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>759629</v>
+        <v>759334</v>
       </c>
       <c r="R14" t="n">
-        <v>7074125</v>
+        <v>7074199</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2183,17 +2129,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre fruktkroppar</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2204,68 +2145,52 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Stående död</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Jessica  Åström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130261257</v>
+        <v>130261223</v>
       </c>
       <c r="B15" t="n">
-        <v>91770</v>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2275,10 +2200,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>759449</v>
+        <v>759450</v>
       </c>
       <c r="R15" t="n">
-        <v>7074314</v>
+        <v>7074279</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2334,12 +2259,12 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Granlåga knäckt</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Picea abies # Granlåga knäckt</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2357,50 +2282,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130261235</v>
+        <v>130261224</v>
       </c>
       <c r="B16" t="n">
-        <v>57859</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>759616</v>
+        <v>759568</v>
       </c>
       <c r="R16" t="n">
-        <v>7074094</v>
+        <v>7074103</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2456,12 +2376,12 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Granhögstubbe knäckt</t>
+          <t>Äldre granlåga</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe knäckt</t>
+          <t>Picea abies # Äldre granlåga</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2479,53 +2399,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130261233</v>
+        <v>130261225</v>
       </c>
       <c r="B17" t="n">
-        <v>58021</v>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>759425</v>
+        <v>759453</v>
       </c>
       <c r="R17" t="n">
-        <v>7074122</v>
+        <v>7074313</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2555,21 +2467,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2578,6 +2480,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Tunnare granlåga invid äldre talltorraka</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies # Tunnare granlåga invid äldre talltorraka</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2594,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130261224</v>
+        <v>130261226</v>
       </c>
       <c r="B18" t="n">
-        <v>91737</v>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,10 +2551,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>759568</v>
+        <v>759410</v>
       </c>
       <c r="R18" t="n">
-        <v>7074103</v>
+        <v>7074242</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2688,12 +2610,12 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Äldre granlåga</t>
+          <t>Granlåga rotknäckt</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies # Äldre granlåga</t>
+          <t>Picea abies # Granlåga rotknäckt</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2711,48 +2633,51 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130261256</v>
+        <v>114558886</v>
       </c>
       <c r="B19" t="n">
-        <v>91770</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>NV Gröthällberget, Vb</t>
+          <t>300m NO Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>759454</v>
+        <v>759614</v>
       </c>
       <c r="R19" t="n">
-        <v>7074134</v>
+        <v>7074148</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2776,12 +2701,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2790,52 +2715,33 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Granstubbe knäckt</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies # Granstubbe knäckt</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Drott</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Drott, Karl-Henrik  Drott</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130261239</v>
+        <v>130261235</v>
       </c>
       <c r="B20" t="n">
-        <v>57859</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2868,10 +2774,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>759521</v>
+        <v>759616</v>
       </c>
       <c r="R20" t="n">
-        <v>7074165</v>
+        <v>7074094</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2927,12 +2833,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granhögstubbe knäckt</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2950,14 +2856,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130261242</v>
+        <v>130261236</v>
       </c>
       <c r="B21" t="n">
-        <v>57859</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2990,10 +2896,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>759521</v>
+        <v>759588</v>
       </c>
       <c r="R21" t="n">
-        <v>7074133</v>
+        <v>7074157</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3028,11 +2934,6 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Vid basen</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3054,12 +2955,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Knäckt gran</t>
+          <t>Granhögstubbe grov, knäckt</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Knäckt gran</t>
+          <t>Picea abies # Granhögstubbe grov, knäckt</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3080,11 +2981,11 @@
         <v>130261237</v>
       </c>
       <c r="B22" t="n">
-        <v>57859</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3204,14 +3105,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130261243</v>
+        <v>130261238</v>
       </c>
       <c r="B23" t="n">
-        <v>57859</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3235,7 +3136,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3244,10 +3145,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>759457</v>
+        <v>759413</v>
       </c>
       <c r="R23" t="n">
-        <v>7074149</v>
+        <v>7074262</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3284,7 +3185,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Kåda</t>
+          <t>Vid basen</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3306,9 +3207,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3326,10 +3232,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130261226</v>
+        <v>130261239</v>
       </c>
       <c r="B24" t="n">
-        <v>91737</v>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3337,34 +3243,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>759410</v>
+        <v>759521</v>
       </c>
       <c r="R24" t="n">
-        <v>7074242</v>
+        <v>7074165</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3420,12 +3331,12 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Granlåga rotknäckt</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga rotknäckt</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3443,27 +3354,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130261231</v>
+        <v>130261240</v>
       </c>
       <c r="B25" t="n">
-        <v>57862</v>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3483,10 +3394,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>759348</v>
+        <v>759411</v>
       </c>
       <c r="R25" t="n">
-        <v>7074185</v>
+        <v>7074135</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3521,11 +3432,6 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på granlåga</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3547,12 +3453,12 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3570,45 +3476,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130261255</v>
+        <v>130261241</v>
       </c>
       <c r="B26" t="n">
-        <v>91770</v>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>759576</v>
+        <v>759358</v>
       </c>
       <c r="R26" t="n">
-        <v>7074103</v>
+        <v>7074193</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3664,12 +3575,12 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Granstubbe knäckt</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe knäckt</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3687,45 +3598,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130261258</v>
+        <v>130261242</v>
       </c>
       <c r="B27" t="n">
-        <v>91770</v>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>759498</v>
+        <v>759521</v>
       </c>
       <c r="R27" t="n">
-        <v>7074364</v>
+        <v>7074133</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3760,6 +3676,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Vid basen</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3781,12 +3702,12 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Knäckt gran</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Picea abies # Knäckt gran</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3804,45 +3725,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130261259</v>
+        <v>130261243</v>
       </c>
       <c r="B28" t="n">
-        <v>91770</v>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>759622</v>
+        <v>759457</v>
       </c>
       <c r="R28" t="n">
-        <v>7074145</v>
+        <v>7074149</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3877,6 +3803,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Kåda</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3896,14 +3827,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>Stående död</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3921,10 +3847,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130261240</v>
+        <v>130261228</v>
       </c>
       <c r="B29" t="n">
-        <v>57859</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3932,16 +3858,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3950,21 +3876,24 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>759411</v>
+        <v>759417</v>
       </c>
       <c r="R29" t="n">
-        <v>7074135</v>
+        <v>7074118</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3999,6 +3928,11 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4020,12 +3954,12 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Stående död</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Stående död</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4043,10 +3977,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130261228</v>
+        <v>130261231</v>
       </c>
       <c r="B30" t="n">
-        <v>57862</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4072,24 +4006,21 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>759417</v>
+        <v>759348</v>
       </c>
       <c r="R30" t="n">
-        <v>7074118</v>
+        <v>7074185</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4126,7 +4057,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på granlåga</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4150,12 +4081,12 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>Stående död</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies # Stående död</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4173,27 +4104,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130261238</v>
+        <v>130261249</v>
       </c>
       <c r="B31" t="n">
-        <v>57859</v>
+        <v>58327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4202,21 +4133,24 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>NV Gröthällberget, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>759413</v>
+        <v>759466</v>
       </c>
       <c r="R31" t="n">
-        <v>7074262</v>
+        <v>7074152</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4246,14 +4180,19 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Vid basen</t>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4264,26 +4203,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies # Levande</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4297,6 +4216,240 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130261233</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>759425</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7074122</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130261234</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>NV Gröthällberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>759386</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7074195</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58829-2025 artfynd.xlsx
+++ b/artfynd/A 58829-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/144677</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261254</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1033,6 +1048,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261255</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1150,6 +1170,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261256</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,6 +1292,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261257</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1384,6 +1414,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261258</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1501,6 +1536,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261259</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1608,6 +1648,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/389140</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1720,6 +1765,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/389141</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1837,6 +1887,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261227</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1954,6 +2009,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261232</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2061,6 +2121,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1586002</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2162,6 +2227,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122748168</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2279,6 +2349,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261223</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2396,6 +2471,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261224</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2513,6 +2593,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261225</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2630,6 +2715,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261226</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2731,6 +2821,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114558886</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2853,6 +2948,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261235</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2975,6 +3075,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261236</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3102,6 +3207,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261237</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3229,6 +3339,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261238</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3351,6 +3466,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261239</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3473,6 +3593,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261240</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3595,6 +3720,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261241</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3722,6 +3852,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261242</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3844,6 +3979,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261243</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3974,6 +4114,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261228</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4101,6 +4246,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261231</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4216,6 +4366,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261249</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4331,6 +4486,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261233</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4450,8 +4610,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130261234</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>